--- a/data/google_news_dedup_audit_01_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_01_0426_UTC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,106 +445,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8917391300201416</v>
+        <v>0.8917390704154968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Schietpartij Anderlecht: slachtoffer kreeg kogel in arm - GVA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Schietpartij Anderlecht: slachtoffer kreeg kogel in arm - Nieuwsblad</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Schietpartij Anderlecht: slachtoffer kreeg kogel in arm - GVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.7553750276565552</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Dutch minor convicted over plans to attack Flemish Parliament - belganewsagency.eu</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Dutch schoolboy convicted of planning terror attack on Flemish Parliament in Brussels - The Brussels Times</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.7251390218734741</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Dutch minor convicted over plans to attack Flemish Parliament - belganewsagency.eu</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>12-year-old Dutch boy planned terrorist attack on the Flemish Parliament - VRT</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B5" t="n">
-        <v>15</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.8774957656860352</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Un enfant de 12 ans planifiait un attentat contre le parlement flamand à Bruxelles - parismatch.be</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Un jeune Néerlandais de 13 ans préparait un attentat contre le Parlement flamand à Bruxelles - BruxellesToday</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B6" t="n">
-        <v>33</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.9807875156402588</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Attentat déjoué contre la Bank of America à Paris : une information judiciaire ouverte pour association de malfaiteurs terroriste - Le Monde.fr</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Attentat déjoué contre Bank of America à Paris : une information judiciaire ouverte pour association de malfaiteurs terroriste - Le Parisien</t>
         </is>
       </c>
     </row>
